--- a/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten</t>
+          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,81</t>
+          <t>3,3; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,02</t>
+          <t>5,43; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,78</t>
+          <t>4,19; 6,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,34 +697,34 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,74</t>
+          <t>4,43; 6,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,29</t>
+          <t>4,2; 5,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,25</t>
+          <t>3,45; 4,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,88</t>
+          <t>5,02; 6,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,53</t>
+          <t>4,34; 5,6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,56</t>
+          <t>4,64; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 5,97</t>
+          <t>4,64; 5,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 5,54</t>
+          <t>4,73; 5,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,59</t>
+          <t>3,18; 4,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,11</t>
+          <t>5,01; 6,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,45</t>
+          <t>4,38; 6,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,03</t>
+          <t>4,14; 5,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 6,02</t>
+          <t>4,97; 6,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,74</t>
+          <t>4,78; 5,65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,97</t>
+          <t>2,87; 5,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 5,47</t>
+          <t>4,73; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,57</t>
+          <t>3,83; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,84</t>
+          <t>5,03; 6,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,83</t>
+          <t>3,49; 4,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 5,21</t>
+          <t>4,55; 5,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,07</t>
+          <t>4,79; 6,05</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,18</t>
+          <t>3,35; 5,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 4,82</t>
+          <t>3,77; 4,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,73</t>
+          <t>5,01; 6,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,46</t>
+          <t>3,29; 4,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,38</t>
+          <t>4,31; 7,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,94</t>
+          <t>4,61; 6,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,49</t>
+          <t>3,43; 4,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 5,94</t>
+          <t>4,23; 5,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,34</t>
+          <t>4,92; 6,42</t>
         </is>
       </c>
     </row>
@@ -1122,49 +1122,49 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,36</t>
+          <t>4,77; 8,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,72</t>
+          <t>6,02; 11,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,26</t>
+          <t>4,25; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,08</t>
+          <t>4,41; 6,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,22</t>
+          <t>4,84; 8,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,61</t>
+          <t>4,32; 5,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,11</t>
+          <t>4,94; 6,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,91</t>
+          <t>5,68; 9,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,55</t>
+          <t>3,47; 4,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,52</t>
+          <t>4,42; 5,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,51</t>
+          <t>6,0; 8,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,0</t>
+          <t>3,75; 6,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,87</t>
+          <t>4,68; 5,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,81</t>
+          <t>6,0; 6,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,92</t>
+          <t>3,73; 5,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,56</t>
+          <t>4,7; 5,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 6,98</t>
+          <t>6,11; 7,08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 4,83</t>
+          <t>4,05; 4,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,12</t>
+          <t>4,29; 5,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,49</t>
+          <t>5,17; 7,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,65</t>
+          <t>4,2; 5,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,53</t>
+          <t>4,67; 5,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,76</t>
+          <t>4,78; 7,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,2</t>
+          <t>4,3; 5,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 5,18</t>
+          <t>4,59; 5,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,03</t>
+          <t>5,28; 7,0</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,63</t>
+          <t>4,57; 5,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,21</t>
+          <t>4,89; 6,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,28</t>
+          <t>4,91; 6,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,84</t>
+          <t>4,71; 6,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,47</t>
+          <t>4,47; 5,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,1</t>
+          <t>4,55; 6,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,02</t>
+          <t>4,77; 5,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,59</t>
+          <t>4,78; 5,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,89</t>
+          <t>4,89; 5,86</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 4,73</t>
+          <t>4,26; 4,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,48</t>
+          <t>4,94; 5,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,12</t>
+          <t>5,32; 6,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 4,99</t>
+          <t>4,32; 5,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,38</t>
+          <t>4,87; 5,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,92</t>
+          <t>5,13; 5,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,34</t>
+          <t>4,96; 5,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 5,85</t>
+          <t>5,31; 5,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,78</t>
+          <t>3,27; 4,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,95</t>
+          <t>5,33; 8,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,52</t>
+          <t>4,2; 6,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,32</t>
+          <t>3,32; 4,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,67</t>
+          <t>4,44; 6,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,2</t>
+          <t>4,17; 5,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,23</t>
+          <t>3,44; 4,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,73</t>
+          <t>5,11; 6,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,6</t>
+          <t>4,31; 5,47</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,59</t>
+          <t>4,64; 5,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,99</t>
+          <t>4,64; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,54</t>
+          <t>4,79; 5,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,64</t>
+          <t>3,28; 4,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,87</t>
+          <t>4,98; 6,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,69</t>
+          <t>4,4; 6,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 5,01</t>
+          <t>4,12; 5,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,05</t>
+          <t>4,99; 6,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,65</t>
+          <t>4,77; 5,7</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,01</t>
+          <t>2,86; 5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,51</t>
+          <t>4,7; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,56</t>
+          <t>3,76; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,08</t>
+          <t>4,09; 5,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,76</t>
+          <t>5,13; 6,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,86</t>
+          <t>3,56; 4,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,18</t>
+          <t>4,55; 5,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,05</t>
+          <t>4,74; 6,04</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,25</t>
+          <t>3,38; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 4,83</t>
+          <t>3,83; 4,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,75</t>
+          <t>5,01; 6,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,39</t>
+          <t>3,32; 4,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,16</t>
+          <t>4,26; 7,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,85</t>
+          <t>4,59; 7,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,38</t>
+          <t>3,46; 4,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,87</t>
+          <t>4,23; 5,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,42</t>
+          <t>4,88; 6,3</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,6</t>
+          <t>4,65; 8,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 11,84</t>
+          <t>5,91; 11,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1137,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,08</t>
+          <t>4,44; 6,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,06</t>
+          <t>4,8; 8,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,66</t>
+          <t>4,27; 5,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,94</t>
+          <t>4,97; 6,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,21</t>
+          <t>5,68; 9,26</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,55</t>
+          <t>4,34; 5,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,06</t>
+          <t>3,74; 5,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,79</t>
+          <t>4,64; 5,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,8</t>
+          <t>6,0; 6,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,03</t>
+          <t>3,71; 4,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,55</t>
+          <t>4,72; 5,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,08</t>
+          <t>6,11; 6,97</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 4,89</t>
+          <t>4,05; 4,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,11</t>
+          <t>4,26; 5,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,37</t>
+          <t>5,18; 7,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,7</t>
+          <t>4,22; 5,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,62</t>
+          <t>4,67; 5,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,56</t>
+          <t>4,79; 7,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,23</t>
+          <t>4,28; 5,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,22</t>
+          <t>4,58; 5,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,0</t>
+          <t>5,25; 7,0</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,56</t>
+          <t>4,62; 5,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,15</t>
+          <t>4,89; 6,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,09</t>
+          <t>4,95; 6,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,85</t>
+          <t>4,75; 6,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,48</t>
+          <t>4,47; 5,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,11</t>
+          <t>4,62; 6,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,97</t>
+          <t>4,8; 5,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,54</t>
+          <t>4,77; 5,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,86</t>
+          <t>4,92; 5,83</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 4,75</t>
+          <t>4,23; 4,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,46</t>
+          <t>4,92; 5,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,14</t>
+          <t>5,35; 6,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,01</t>
+          <t>4,34; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,37</t>
+          <t>4,86; 5,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,13; 5,94</t>
+          <t>5,1; 5,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,35</t>
+          <t>4,95; 5,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">

--- a/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,35</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,91</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,7</t>
+          <t>3,32; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,07</t>
+          <t>4,47; 6,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,67</t>
+          <t>4,17; 5,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,38</t>
+          <t>3,3; 4,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,7</t>
+          <t>5,37; 8,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,27</t>
+          <t>4,2; 6,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,24</t>
+          <t>3,41; 4,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,91</t>
+          <t>5,11; 6,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,47</t>
+          <t>4,33; 5,53</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,06</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,63</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,16</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,02</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,27</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,13</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,51</t>
+          <t>3,24; 4,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,02</t>
+          <t>5,0; 7,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,51</t>
+          <t>4,35; 6,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,7</t>
+          <t>4,6; 5,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,82</t>
+          <t>4,65; 5,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,76</t>
+          <t>4,74; 5,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,0</t>
+          <t>4,19; 5,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 6,09</t>
+          <t>4,93; 6,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,7</t>
+          <t>4,75; 5,74</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,12</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,0</t>
+          <t>3,75; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,52</t>
+          <t>4,17; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>5,03; 6,84</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2,94; 4,97</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4,72; 5,47</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>4,0; 5,67</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,76; 5,56</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,09; 5,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,13; 6,86</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,86</t>
+          <t>3,54; 4,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,19</t>
+          <t>4,58; 5,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,04</t>
+          <t>4,75; 6,07</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,91</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,12</t>
+          <t>3,35; 4,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,97</t>
+          <t>4,24; 7,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,71</t>
+          <t>4,6; 6,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,41</t>
+          <t>3,38; 5,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,03</t>
+          <t>3,8; 4,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,24</t>
+          <t>4,98; 6,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,41</t>
+          <t>3,47; 4,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,8</t>
+          <t>4,25; 5,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 6,3</t>
+          <t>4,91; 6,34</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,92</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,91</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4,25; 6,26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4,44; 6,08</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4,85; 8,22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3,88; 5,23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,65; 8,24</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,91; 11,56</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 6,36</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,09</t>
+          <t>4,66; 8,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,08</t>
+          <t>6,12; 11,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,59</t>
+          <t>4,32; 5,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,96</t>
+          <t>5,0; 7,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,26</t>
+          <t>5,58; 8,91</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,23</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,39</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3,89</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,5</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,23</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,39</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,62</t>
+          <t>3,75; 6,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,48</t>
+          <t>4,64; 5,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,0</t>
+          <t>6,0; 6,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,96</t>
+          <t>3,47; 4,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,89</t>
+          <t>4,37; 5,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,81</t>
+          <t>6,0; 7,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,9</t>
+          <t>3,71; 4,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 5,56</t>
+          <t>4,68; 5,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,97</t>
+          <t>6,1; 6,98</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,66</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,14</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,99</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 4,88</t>
+          <t>4,23; 5,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,12</t>
+          <t>4,64; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,4</t>
+          <t>4,84; 7,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,63</t>
+          <t>4,05; 4,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,52</t>
+          <t>4,24; 5,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,62</t>
+          <t>5,24; 7,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,23</t>
+          <t>4,33; 5,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 5,24</t>
+          <t>4,58; 5,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,0</t>
+          <t>5,29; 7,03</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,39</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,87</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5,15</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>5,04</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>5,42</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5,42</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,87</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,58</t>
+          <t>4,69; 6,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,16</t>
+          <t>4,48; 5,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,14</t>
+          <t>4,53; 6,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,95</t>
+          <t>4,6; 5,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,44</t>
+          <t>4,87; 6,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,33</t>
+          <t>5,0; 6,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,99</t>
+          <t>4,8; 6,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,57</t>
+          <t>4,77; 5,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,83</t>
+          <t>4,9; 5,89</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,62</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,46</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,18</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,67</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 4,75</t>
+          <t>4,36; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,47</t>
+          <t>4,87; 5,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,08</t>
+          <t>5,1; 5,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,0</t>
+          <t>4,24; 4,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,37</t>
+          <t>4,92; 5,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,95</t>
+          <t>5,32; 6,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,33</t>
+          <t>4,97; 5,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,31; 5,88</t>
+          <t>5,33; 5,85</t>
         </is>
       </c>
     </row>
